--- a/outputs/daily/hr_rankings_2026-07-29.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-29.xlsx
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>64.8</v>
+        <v>64.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>57.6</v>
+        <v>56.2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -23970,7 +23970,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
@@ -23980,7 +23980,7 @@
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/18, 0 HR</t>
+          <t>Last 7 games: 1/19, 0 HR</t>
         </is>
       </c>
       <c r="AL85" t="inlineStr">
@@ -26084,7 +26084,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -31648,7 +31648,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -31924,7 +31924,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -32459,32 +32459,32 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>596142</t>
+          <t>605137</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Gary Sánchez</t>
+          <t>Josh Bell</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-29T19:45:00Z</t>
+          <t>2026-07-29T23:40:00Z</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -32494,12 +32494,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Randy Dobnak</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>677976</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -32522,58 +32522,62 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>42</v>
+        <v>44.7</v>
       </c>
       <c r="Q116" t="n">
-        <v>31</v>
+        <v>36.7</v>
       </c>
       <c r="R116" t="n">
-        <v>52.8</v>
+        <v>27.1</v>
       </c>
       <c r="S116" t="n">
-        <v>86.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T116" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U116" t="n">
         <v>14.1</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W116" t="inlineStr">
+      <c r="Z116" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC116" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -32593,12 +32597,12 @@
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -32608,12 +32612,12 @@
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/14, 0 HR</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL116" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.4% barrel, 10.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.4% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
@@ -32623,112 +32627,104 @@
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>42.26</t>
+          <t>44.27</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>101.0026</t>
+          <t>100.9921</t>
         </is>
       </c>
       <c r="AR116" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>0.4472</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>0.2006</t>
+          <t>0.1989</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr">
         <is>
-          <t>0.3514</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>72.19</t>
+          <t>72.26</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>28.18</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>44.37</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>28.84</t>
+          <t>26.22</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>0.2052</t>
+          <t>0.1716</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>39.99</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>92.02</t>
         </is>
       </c>
       <c r="BD116" t="inlineStr">
         <is>
-          <t>0.385</t>
+          <t>0.429</t>
         </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
-          <t>0.1303</t>
+          <t>0.1422</t>
         </is>
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>19.14</t>
-        </is>
-      </c>
-      <c r="BG116" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH116" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="BG116" t="inlineStr"/>
+      <c r="BH116" t="inlineStr"/>
       <c r="BI116" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ116" t="inlineStr"/>
@@ -32739,22 +32735,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>605137</t>
+          <t>669224</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Josh Bell</t>
+          <t>Austin Wells</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -32764,22 +32760,22 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Randy Dobnak</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>677976</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -32802,26 +32798,26 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>44.7</v>
+        <v>36.5</v>
       </c>
       <c r="Q117" t="n">
-        <v>36.7</v>
+        <v>41.4</v>
       </c>
       <c r="R117" t="n">
-        <v>27.1</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="S117" t="n">
-        <v>81.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T117" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U117" t="n">
-        <v>14.1</v>
+        <v>37.8</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -32835,7 +32831,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
@@ -32877,27 +32873,27 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 0 HR</t>
+          <t>Last 7 games: 4/16, 1 HR</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.4% barrel, 1.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
@@ -32907,104 +32903,112 @@
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>7.82</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>44.27</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>89.34</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>100.9921</t>
+          <t>100.4941</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
         <is>
-          <t>0.4472</t>
+          <t>0.3745</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>0.1989</t>
+          <t>0.1612</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.2961</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>72.26</t>
+          <t>72.98</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>28.18</t>
+          <t>27.77</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>46.73</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>26.22</t>
+          <t>32.79</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>0.1716</t>
+          <t>0.1414</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>44.46</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>92.02</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD117" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.4167</t>
         </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
-          <t>0.1422</t>
+          <t>0.1489</t>
         </is>
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>17.86</t>
-        </is>
-      </c>
-      <c r="BG117" t="inlineStr"/>
-      <c r="BH117" t="inlineStr"/>
+          <t>22.08</t>
+        </is>
+      </c>
+      <c r="BG117" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH117" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="BI117" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ117" t="inlineStr"/>
@@ -33015,32 +33019,32 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>669224</t>
+          <t>701358</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Austin Wells</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-29T23:40:00Z</t>
+          <t>2026-07-30T01:38:00Z</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -33050,12 +33054,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -33078,26 +33082,26 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Pitcher Vulnerable</t>
         </is>
       </c>
       <c r="P118" t="n">
-        <v>36.5</v>
+        <v>42.4</v>
       </c>
       <c r="Q118" t="n">
-        <v>41.4</v>
+        <v>71.8</v>
       </c>
       <c r="R118" t="n">
-        <v>65.09999999999999</v>
+        <v>28.2</v>
       </c>
       <c r="S118" t="n">
         <v>40.2</v>
       </c>
       <c r="T118" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U118" t="n">
-        <v>37.8</v>
+        <v>18.3</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -33136,7 +33140,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr"/>
@@ -33153,12 +33157,12 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
@@ -33168,127 +33172,119 @@
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/16, 1 HR</t>
+          <t>Last 7 games: 1/14, 1 HR</t>
         </is>
       </c>
       <c r="AL118" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.5% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>7.82</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.18</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>89.34</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>100.4941</t>
+          <t>101.4789</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
         <is>
-          <t>0.3745</t>
+          <t>0.4187</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>0.1612</t>
+          <t>0.1781</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>0.2961</t>
+          <t>0.3222</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>27.77</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>46.73</t>
+          <t>36.72</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>32.79</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>0.1414</t>
+          <t>0.1451</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="BD118" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t>0.563</t>
         </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
-          <t>0.1489</t>
+          <t>0.242</t>
         </is>
       </c>
       <c r="BF118" t="inlineStr">
         <is>
-          <t>22.08</t>
-        </is>
-      </c>
-      <c r="BG118" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH118" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>30.1</t>
+        </is>
+      </c>
+      <c r="BG118" t="inlineStr"/>
+      <c r="BH118" t="inlineStr"/>
       <c r="BI118" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ118" t="inlineStr"/>
@@ -33299,47 +33295,47 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>596142</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Gary Sánchez</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-30T01:38:00Z</t>
+          <t>2026-07-29T19:45:00Z</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -33348,7 +33344,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
@@ -33362,65 +33358,61 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Pitcher Vulnerable</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P119" t="n">
-        <v>42.4</v>
+        <v>42</v>
       </c>
       <c r="Q119" t="n">
-        <v>71.8</v>
+        <v>31</v>
       </c>
       <c r="R119" t="n">
-        <v>28.2</v>
+        <v>52.8</v>
       </c>
       <c r="S119" t="n">
-        <v>40.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T119" t="n">
         <v>50</v>
       </c>
       <c r="U119" t="n">
-        <v>18.3</v>
+        <v>12</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr"/>
@@ -33437,134 +33429,142 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/14, 1 HR</t>
+          <t>Last 7 games: 3/15, 0 HR</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.5% barrel, 7.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.4% barrel, 10.5 HR allowed</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>43.18</t>
+          <t>42.26</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>101.4789</t>
+          <t>101.0026</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>0.4187</t>
+          <t>0.435</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>0.1781</t>
+          <t>0.2006</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>0.3222</t>
+          <t>0.3514</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>72.19</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>36.72</t>
+          <t>44.37</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>28.84</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>0.1451</t>
+          <t>0.2052</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>39.99</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="BD119" t="inlineStr">
         <is>
-          <t>0.563</t>
+          <t>0.385</t>
         </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>0.1303</t>
         </is>
       </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>30.1</t>
-        </is>
-      </c>
-      <c r="BG119" t="inlineStr"/>
-      <c r="BH119" t="inlineStr"/>
+          <t>19.14</t>
+        </is>
+      </c>
+      <c r="BG119" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH119" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
       <c r="BI119" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ119" t="inlineStr"/>
@@ -38596,7 +38596,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -42171,47 +42171,47 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>668904</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Royce Lewis</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-07-29T19:45:00Z</t>
+          <t>2026-07-29T23:40:00Z</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Randy Dobnak</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>677976</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -42234,61 +42234,65 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P151" t="n">
-        <v>26.6</v>
+        <v>41.6</v>
       </c>
       <c r="Q151" t="n">
-        <v>29.9</v>
+        <v>36.9</v>
       </c>
       <c r="R151" t="n">
-        <v>52.8</v>
+        <v>27.1</v>
       </c>
       <c r="S151" t="n">
-        <v>64.3</v>
+        <v>71.7</v>
       </c>
       <c r="T151" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U151" t="n">
-        <v>39.7</v>
+        <v>8.1</v>
       </c>
       <c r="V151" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W151" t="inlineStr">
+      <c r="Z151" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr"/>
@@ -42305,12 +42309,12 @@
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
@@ -42320,12 +42324,12 @@
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Contact streak: 5/13 over last 7 games</t>
+          <t>Last 7 games: 4/23, 0 HR</t>
         </is>
       </c>
       <c r="AL151" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.4% barrel, 10.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.4% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
@@ -42335,112 +42339,104 @@
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>98.6797</t>
+          <t>100.6159</t>
         </is>
       </c>
       <c r="AR151" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>0.3923</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>0.1649</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.44</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>47.99</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>31.13</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>0.1657</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>39.99</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>92.02</t>
         </is>
       </c>
       <c r="BD151" t="inlineStr">
         <is>
-          <t>0.385</t>
+          <t>0.429</t>
         </is>
       </c>
       <c r="BE151" t="inlineStr">
         <is>
-          <t>0.1303</t>
+          <t>0.1422</t>
         </is>
       </c>
       <c r="BF151" t="inlineStr">
         <is>
-          <t>19.14</t>
-        </is>
-      </c>
-      <c r="BG151" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH151" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="BG151" t="inlineStr"/>
+      <c r="BH151" t="inlineStr"/>
       <c r="BI151" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ151" t="inlineStr"/>
@@ -42451,27 +42447,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>668904</t>
+          <t>691016</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Royce Lewis</t>
+          <t>Tyler Soderstrom</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-07-29T23:40:00Z</t>
+          <t>2026-07-30T01:40:00Z</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -42481,22 +42477,22 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Randy Dobnak</t>
+          <t>Patrick Sandoval</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>677976</t>
+          <t>663776</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -42514,26 +42510,26 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>41.6</v>
+        <v>44.5</v>
       </c>
       <c r="Q152" t="n">
-        <v>36.9</v>
+        <v>11.3</v>
       </c>
       <c r="R152" t="n">
-        <v>27.1</v>
+        <v>30.9</v>
       </c>
       <c r="S152" t="n">
-        <v>71.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T152" t="n">
         <v>50</v>
       </c>
       <c r="U152" t="n">
-        <v>8.1</v>
+        <v>42.3</v>
       </c>
       <c r="V152" t="inlineStr">
         <is>
@@ -42547,7 +42543,7 @@
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
@@ -42572,7 +42568,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr"/>
@@ -42589,27 +42585,27 @@
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 0 HR</t>
+          <t>Last 7 games: 7/25, 1 HR</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.4% barrel, 1.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 2.1% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
@@ -42619,104 +42615,104 @@
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>100.6159</t>
+          <t>101.9156</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.4318</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>0.1649</t>
+          <t>0.1757</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.3382</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>74.44</t>
+          <t>74.28</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>36.07</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>31.13</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>0.1657</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>92.02</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="BD152" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="BE152" t="inlineStr">
         <is>
-          <t>0.1422</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="BG152" t="inlineStr"/>
       <c r="BH152" t="inlineStr"/>
       <c r="BI152" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ152" t="inlineStr"/>
@@ -42727,56 +42723,56 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>691016</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Tyler Soderstrom</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-07-30T01:40:00Z</t>
+          <t>2026-07-29T19:45:00Z</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Patrick Sandoval</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>663776</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
@@ -42790,65 +42786,61 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P153" t="n">
-        <v>44.5</v>
+        <v>26.6</v>
       </c>
       <c r="Q153" t="n">
-        <v>11.3</v>
+        <v>29.9</v>
       </c>
       <c r="R153" t="n">
-        <v>30.9</v>
+        <v>52.8</v>
       </c>
       <c r="S153" t="n">
-        <v>92.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T153" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U153" t="n">
-        <v>42.3</v>
+        <v>35.6</v>
       </c>
       <c r="V153" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr"/>
@@ -42865,27 +42857,27 @@
       </c>
       <c r="AH153" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 1 HR</t>
+          <t>Contact streak: 5/14 over last 7 games</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 2.1% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.4% barrel, 10.5 HR allowed</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
@@ -42895,104 +42887,112 @@
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>101.9156</t>
+          <t>98.6797</t>
         </is>
       </c>
       <c r="AR153" t="inlineStr">
         <is>
-          <t>0.4318</t>
+          <t>0.419</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>0.1757</t>
+          <t>0.099</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr">
         <is>
-          <t>0.3382</t>
+          <t>0.373</t>
         </is>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>74.28</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.158</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>39.99</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="BD153" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>0.385</t>
         </is>
       </c>
       <c r="BE153" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.1303</t>
         </is>
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>21.3</t>
-        </is>
-      </c>
-      <c r="BG153" t="inlineStr"/>
-      <c r="BH153" t="inlineStr"/>
+          <t>19.14</t>
+        </is>
+      </c>
+      <c r="BG153" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH153" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
       <c r="BI153" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ153" t="inlineStr"/>
@@ -43304,7 +43304,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -43588,7 +43588,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -47412,7 +47412,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -53240,7 +53240,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -59088,7 +59088,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -63228,7 +63228,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -63252,7 +63252,7 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>30.5</v>
+        <v>30.9</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
@@ -63285,7 +63285,7 @@
         <v>80</v>
       </c>
       <c r="U227" t="n">
-        <v>16.6</v>
+        <v>24.9</v>
       </c>
       <c r="V227" t="inlineStr">
         <is>
@@ -63341,12 +63341,12 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ227" t="inlineStr">
@@ -63356,7 +63356,7 @@
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/13, 0 HR</t>
+          <t>Last 7 games: 4/14, 0 HR</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
@@ -66890,7 +66890,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -66914,7 +66914,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>64.8</v>
+        <v>64.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -66947,7 +66947,7 @@
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>57.6</v>
+        <v>56.2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -67004,7 +67004,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -68826,7 +68826,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-07-29.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-29.xlsx
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -17840,7 +17840,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -20640,7 +20640,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -21760,7 +21760,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -22040,7 +22040,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -23160,7 +23160,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -23440,7 +23440,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -24000,7 +24000,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -24280,7 +24280,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -25400,7 +25400,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -25680,7 +25680,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -26240,7 +26240,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -26520,7 +26520,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -27080,7 +27080,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -27360,7 +27360,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -27640,7 +27640,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -28760,7 +28760,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -29320,7 +29320,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -29600,7 +29600,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -29880,7 +29880,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -30160,7 +30160,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -31886,7 +31886,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -32446,7 +32446,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -33006,7 +33006,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -33286,7 +33286,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -34966,7 +34966,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -35526,7 +35526,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -36366,7 +36366,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
